--- a/artfynd/A 25212-2025 artfynd.xlsx
+++ b/artfynd/A 25212-2025 artfynd.xlsx
@@ -808,10 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124531362</v>
+        <v>124531660</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>83424</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,29 +820,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -851,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>393295</v>
+        <v>393310</v>
       </c>
       <c r="R3" t="n">
-        <v>6692540</v>
+        <v>6692530</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,6 +897,11 @@
           <t>2025-04-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ny dellokal.  Alla äldre granar döda av granbarkborre, än så länge stående som torrträd. Fruktkropparna begravda under en matta av döda barr och smågrenar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -910,7 +923,11 @@
           <t>Agnes Rengren</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124531660</v>
+        <v>124531362</v>
       </c>
       <c r="B5" t="n">
-        <v>83424</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,37 +1066,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1445</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1088,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>393310</v>
+        <v>393295</v>
       </c>
       <c r="R5" t="n">
-        <v>6692530</v>
+        <v>6692540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,11 +1135,6 @@
           <t>2025-04-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ny dellokal.  Alla äldre granar döda av granbarkborre, än så länge stående som torrträd. Fruktkropparna begravda under en matta av döda barr och smågrenar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1152,11 +1156,7 @@
           <t>Agnes Rengren</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/artfynd/A 25212-2025 artfynd.xlsx
+++ b/artfynd/A 25212-2025 artfynd.xlsx
@@ -931,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124531565</v>
+        <v>124531362</v>
       </c>
       <c r="B4" t="n">
-        <v>83424</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,37 +943,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1445</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -982,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>393227</v>
+        <v>393295</v>
       </c>
       <c r="R4" t="n">
-        <v>6692505</v>
+        <v>6692540</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,11 +1012,6 @@
           <t>2025-04-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Några torrgranar av granbarkborre.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1046,18 +1033,14 @@
           <t>Agnes Rengren</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124531362</v>
+        <v>124531565</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>83424</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,29 +1049,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1097,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>393295</v>
+        <v>393227</v>
       </c>
       <c r="R5" t="n">
-        <v>6692540</v>
+        <v>6692505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,6 +1126,11 @@
           <t>2025-04-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Några torrgranar av granbarkborre.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1156,7 +1152,11 @@
           <t>Agnes Rengren</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/artfynd/A 25212-2025 artfynd.xlsx
+++ b/artfynd/A 25212-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>125071930</v>
       </c>
       <c r="B6" t="n">
-        <v>83424</v>
+        <v>83564</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 25212-2025 artfynd.xlsx
+++ b/artfynd/A 25212-2025 artfynd.xlsx
@@ -1163,12 +1163,7 @@
         <v>125071930</v>
       </c>
       <c r="B6" t="n">
-        <v>83564</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25212-2025 artfynd.xlsx
+++ b/artfynd/A 25212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>58436692</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393225.2639368131</v>
+        <v>393225</v>
       </c>
       <c r="R2" t="n">
-        <v>6692507.110427567</v>
+        <v>6692507</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,19 +753,9 @@
           <t>2016-04-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-04-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,19 +793,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124531660</v>
+        <v>58572202</v>
       </c>
       <c r="B3" t="n">
-        <v>83424</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -843,7 +823,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,20 +832,19 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ljusnan NV om Mon, Vrm</t>
+          <t>Ljusnan, 1,8 km SSV Osebolskojan lok. 5, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>393310</v>
+        <v>393207</v>
       </c>
       <c r="R3" t="n">
-        <v>6692530</v>
+        <v>6692474</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,17 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2016-04-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ny dellokal.  Alla äldre granar döda av granbarkborre, än så länge stående som torrträd. Fruktkropparna begravda under en matta av döda barr och smågrenar.</t>
+          <t>Inga näringskrävande växter i närheten. Gäller även fyra närliggande lokaler.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,75 +891,84 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Under stora granar</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>granförna - barr och små kvistar</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>Rolf Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124531362</v>
+        <v>82172347</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljusnan NV om Mon, Vrm</t>
+          <t>Ljusnan, 1,8 km SSV Osebolskojan, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>393295</v>
+        <v>393210</v>
       </c>
       <c r="R4" t="n">
-        <v>6692540</v>
+        <v>6692469</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,12 +992,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bedömt som fyra mycel: 9, 3, 1, resp. 1 fruktkropp, räknat från söder.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,31 +1018,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124531565</v>
+        <v>100348726</v>
       </c>
       <c r="B5" t="n">
-        <v>83424</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1072,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,20 +1069,19 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ljusnan NV om Mon, Vrm</t>
+          <t>Torsby, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>393227</v>
+        <v>393204</v>
       </c>
       <c r="R5" t="n">
-        <v>6692505</v>
+        <v>6692480</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,17 +1105,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Några torrgranar av granbarkborre.</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,37 +1119,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agnes Rengren</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125071930</v>
+        <v>124531565</v>
       </c>
       <c r="B6" t="n">
-        <v>83606</v>
+        <v>84158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1190,7 +1167,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>393292</v>
+        <v>393227</v>
       </c>
       <c r="R6" t="n">
-        <v>6692646</v>
+        <v>6692505</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,17 +1213,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I ung granplantage. Fynden intill är i gamla hänsynsytor.</t>
+          <t>Några torrgranar av granbarkborre.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,9 +1249,346 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124531660</v>
+      </c>
+      <c r="B7" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ljusnan NV om Mon, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>393310</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6692530</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ny dellokal.  Alla äldre granar döda av granbarkborre, än så länge stående som torrträd. Fruktkropparna begravda under en matta av döda barr och smågrenar.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125071930</v>
+      </c>
+      <c r="B8" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ljusnan NV om Mon, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>393292</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6692646</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I ung granplantage. Fynden intill är i gamla hänsynsytor.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124531362</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ljusnan NV om Mon, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>393295</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6692540</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25212-2025 artfynd.xlsx
+++ b/artfynd/A 25212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58436692</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58572202</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82172347</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100348726</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124531565</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1370,6 +1400,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124531660</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125071930</t>
         </is>
       </c>
     </row>
@@ -1589,8 +1629,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124531362</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>